--- a/data/trans_orig/IP08-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP08-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4090</t>
+          <t>3996</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>13925</t>
+          <t>13204</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>15,32%</t>
+          <t>14,53%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6808</t>
+          <t>6105</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>16838</t>
+          <t>16232</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>7,03%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>19,39%</t>
+          <t>18,69%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>12430</t>
+          <t>12192</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>26213</t>
+          <t>26648</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>15,0%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>76942</t>
+          <t>77663</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>86777</t>
+          <t>86871</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>84,68%</t>
+          <t>85,47%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,5%</t>
+          <t>95,6%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>70007</t>
+          <t>70613</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>80037</t>
+          <t>80740</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>80,61%</t>
+          <t>81,31%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>92,16%</t>
+          <t>92,97%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>151499</t>
+          <t>151064</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>165282</t>
+          <t>165520</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>85,25%</t>
+          <t>85,0%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>93,01%</t>
+          <t>93,14%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>22968</t>
+          <t>22996</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>39662</t>
+          <t>39833</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>9,57%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>42902</t>
+          <t>43465</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>64068</t>
+          <t>64741</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>9,13%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>13,45%</t>
+          <t>13,59%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>70922</t>
+          <t>70963</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>98691</t>
+          <t>99720</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1166,7 +1166,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>11,06%</t>
+          <t>11,17%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>376425</t>
+          <t>376254</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>393119</t>
+          <t>393091</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>90,47%</t>
+          <t>90,43%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,48%</t>
+          <t>94,47%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>412228</t>
+          <t>411555</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>433394</t>
+          <t>432831</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>86,55%</t>
+          <t>86,41%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>90,99%</t>
+          <t>90,87%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>793692</t>
+          <t>792663</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>821461</t>
+          <t>821420</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>88,94%</t>
+          <t>88,83%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>12270</t>
+          <t>12407</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>25372</t>
+          <t>25374</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,7 +1434,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>14166</t>
+          <t>14054</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>26892</t>
+          <t>27324</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>8,89%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>17,01%</t>
+          <t>17,28%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>28150</t>
+          <t>28519</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>47528</t>
+          <t>47400</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>14,31%</t>
+          <t>14,27%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>148694</t>
+          <t>148692</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>161796</t>
+          <t>161659</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1552,7 +1552,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>92,95%</t>
+          <t>92,87%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>131246</t>
+          <t>130814</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>143972</t>
+          <t>144084</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>82,99%</t>
+          <t>82,72%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>91,04%</t>
+          <t>91,11%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>284677</t>
+          <t>284805</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>304055</t>
+          <t>303686</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>85,69%</t>
+          <t>85,73%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>91,53%</t>
+          <t>91,42%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>44360</t>
+          <t>45465</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>69145</t>
+          <t>68573</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>10,07%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>70873</t>
+          <t>68929</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>98430</t>
+          <t>97324</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>9,56%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>13,65%</t>
+          <t>13,49%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>122752</t>
+          <t>120248</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>158112</t>
+          <t>157045</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,28%</t>
+          <t>11,2%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>611876</t>
+          <t>612448</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>636661</t>
+          <t>635556</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>89,85%</t>
+          <t>89,93%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>93,49%</t>
+          <t>93,32%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>622849</t>
+          <t>623955</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>650406</t>
+          <t>652350</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>86,35%</t>
+          <t>86,51%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>90,17%</t>
+          <t>90,44%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1244188</t>
+          <t>1245255</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1279548</t>
+          <t>1282052</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>88,72%</t>
+          <t>88,8%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>91,25%</t>
+          <t>91,42%</t>
         </is>
       </c>
     </row>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8082</t>
+          <t>8232</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>18712</t>
+          <t>19062</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>20,26%</t>
+          <t>20,64%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>7174</t>
+          <t>7111</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>18414</t>
+          <t>17583</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>21,36%</t>
+          <t>20,4%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>17649</t>
+          <t>17433</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>32216</t>
+          <t>33074</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>9,76%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>18,04%</t>
+          <t>18,52%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>73657</t>
+          <t>73307</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>84287</t>
+          <t>84137</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>79,74%</t>
+          <t>79,36%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>91,25%</t>
+          <t>91,09%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>67778</t>
+          <t>68609</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>79018</t>
+          <t>79081</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>78,64%</t>
+          <t>79,6%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>91,68%</t>
+          <t>91,75%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>146345</t>
+          <t>145487</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>160912</t>
+          <t>161128</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>81,96%</t>
+          <t>81,48%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>90,12%</t>
+          <t>90,24%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>44510</t>
+          <t>44663</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>66749</t>
+          <t>67524</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>9,88%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>14,76%</t>
+          <t>14,93%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>58073</t>
+          <t>58141</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>83580</t>
+          <t>83638</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11,75%</t>
+          <t>11,76%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>16,9%</t>
+          <t>16,92%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>107453</t>
+          <t>110172</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>143039</t>
+          <t>144729</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>11,64%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>15,11%</t>
+          <t>15,29%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>385461</t>
+          <t>384686</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>407700</t>
+          <t>407547</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>85,24%</t>
+          <t>85,07%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>90,16%</t>
+          <t>90,12%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>410866</t>
+          <t>410808</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>436373</t>
+          <t>436305</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>83,1%</t>
+          <t>83,08%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>88,25%</t>
+          <t>88,24%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>803617</t>
+          <t>801927</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>839203</t>
+          <t>836484</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>84,89%</t>
+          <t>84,71%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>88,65%</t>
+          <t>88,36%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9878</t>
+          <t>9888</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>22134</t>
+          <t>21819</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3042,77 +3042,77 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
+          <t>13,14%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>20474</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>13433</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>28413</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>11,89%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>7,8%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>16,5%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>35714</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>27316</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>45110</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>10,56%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>8,07%</t>
+        </is>
+      </c>
+      <c r="W10" s="2" t="inlineStr">
+        <is>
           <t>13,33%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>20474</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>13725</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>28038</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>11,89%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>7,97%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>16,28%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>35714</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>27543</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>46783</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>10,56%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>8,14%</t>
-        </is>
-      </c>
-      <c r="W10" s="2" t="inlineStr">
-        <is>
-          <t>13,83%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>143944</t>
+          <t>144259</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>156200</t>
+          <t>156190</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,82 +3150,82 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
+          <t>86,86%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>94,05%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>216</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>151754</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>143815</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>158795</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>88,11%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>83,5%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>92,2%</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>428</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>302593</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>293197</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>310991</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>89,44%</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
           <t>86,67%</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>94,05%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>216</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>151754</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>144190</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>158503</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>88,11%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>83,72%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>92,03%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>428</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>302593</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>291524</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>310764</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>89,44%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>86,17%</t>
-        </is>
-      </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>91,86%</t>
+          <t>91,93%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>70716</t>
+          <t>69593</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>97881</t>
+          <t>97242</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>9,79%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>13,77%</t>
+          <t>13,68%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>87568</t>
+          <t>87653</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>119466</t>
+          <t>118574</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,63%</t>
+          <t>11,64%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,87%</t>
+          <t>15,75%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>164687</t>
+          <t>165828</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>206097</t>
+          <t>207723</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>11,33%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>14,08%</t>
+          <t>14,19%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>612776</t>
+          <t>613415</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>639941</t>
+          <t>641064</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>86,23%</t>
+          <t>86,32%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>90,05%</t>
+          <t>90,21%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>633400</t>
+          <t>634292</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>665298</t>
+          <t>665213</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>84,13%</t>
+          <t>84,25%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>88,37%</t>
+          <t>88,36%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1257426</t>
+          <t>1255800</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1298836</t>
+          <t>1297695</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>85,92%</t>
+          <t>85,81%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>88,75%</t>
+          <t>88,67%</t>
         </is>
       </c>
     </row>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1874</t>
+          <t>1836</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8302</t>
+          <t>8526</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>13,98%</t>
+          <t>14,36%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>712</t>
+          <t>686</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6445</t>
+          <t>6799</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3679</t>
+          <t>3789</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>12127</t>
+          <t>12610</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>9,85%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>51076</t>
+          <t>50852</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>57504</t>
+          <t>57542</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>86,02%</t>
+          <t>85,64%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,84%</t>
+          <t>96,91%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>62169</t>
+          <t>61815</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>67902</t>
+          <t>67928</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>90,61%</t>
+          <t>90,09%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,96%</t>
+          <t>99,0%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>115866</t>
+          <t>115383</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>124314</t>
+          <t>124204</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>90,53%</t>
+          <t>90,15%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,13%</t>
+          <t>97,04%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>22434</t>
+          <t>23868</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>41373</t>
+          <t>41580</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>29370</t>
+          <t>29445</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>48729</t>
+          <t>50360</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>10,35%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>58185</t>
+          <t>57677</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>85807</t>
+          <t>84476</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>8,82%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>429675</t>
+          <t>429468</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>448614</t>
+          <t>447180</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,22%</t>
+          <t>91,17%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,24%</t>
+          <t>94,93%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>437612</t>
+          <t>435981</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>456971</t>
+          <t>456896</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>89,98%</t>
+          <t>89,65%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,96%</t>
+          <t>93,95%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>871583</t>
+          <t>872914</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>899205</t>
+          <t>899713</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,04%</t>
+          <t>91,18%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,92%</t>
+          <t>93,98%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7212</t>
+          <t>6974</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>17799</t>
+          <t>17652</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>10,27%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5974</t>
+          <t>5904</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>16652</t>
+          <t>16546</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>8,86%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>15526</t>
+          <t>14610</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>30210</t>
+          <t>29946</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>8,35%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>154003</t>
+          <t>154150</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>164590</t>
+          <t>164828</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>89,64%</t>
+          <t>89,73%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,8%</t>
+          <t>95,94%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>170164</t>
+          <t>170270</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>180842</t>
+          <t>180912</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>91,09%</t>
+          <t>91,14%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,8%</t>
+          <t>96,84%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>328408</t>
+          <t>328672</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>343092</t>
+          <t>344008</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>91,58%</t>
+          <t>91,65%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,67%</t>
+          <t>95,93%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>37149</t>
+          <t>37234</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>58633</t>
+          <t>59554</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>41248</t>
+          <t>40454</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>63708</t>
+          <t>62554</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>82772</t>
+          <t>83244</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>114153</t>
+          <t>115865</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>8,02%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>643595</t>
+          <t>642674</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>665079</t>
+          <t>664994</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,65%</t>
+          <t>91,52%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,71%</t>
+          <t>94,7%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>678064</t>
+          <t>679218</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>700524</t>
+          <t>701318</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,41%</t>
+          <t>91,57%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,44%</t>
+          <t>94,55%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1329847</t>
+          <t>1328135</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1361228</t>
+          <t>1360756</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,09%</t>
+          <t>91,98%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,27%</t>
+          <t>94,24%</t>
         </is>
       </c>
     </row>
@@ -5542,12 +5542,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2913</t>
+          <t>2628</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>25527</t>
+          <t>24815</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5557,12 +5557,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>46,69%</t>
+          <t>45,38%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6674</t>
+          <t>6143</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>17506</t>
+          <t>16606</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5592,12 +5592,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>28,23%</t>
+          <t>26,78%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>12544</t>
+          <t>12397</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>38287</t>
+          <t>34551</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5627,12 +5627,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>32,81%</t>
+          <t>29,61%</t>
         </is>
       </c>
     </row>
@@ -5655,12 +5655,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>29151</t>
+          <t>29863</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>51765</t>
+          <t>52050</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5670,12 +5670,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>53,31%</t>
+          <t>54,62%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>94,67%</t>
+          <t>95,19%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>44498</t>
+          <t>45398</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>55330</t>
+          <t>55861</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5705,12 +5705,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>71,77%</t>
+          <t>73,22%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>89,24%</t>
+          <t>90,09%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>78395</t>
+          <t>82131</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>104138</t>
+          <t>104285</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>67,19%</t>
+          <t>70,39%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>89,25%</t>
+          <t>89,38%</t>
         </is>
       </c>
     </row>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>26974</t>
+          <t>27995</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>48276</t>
+          <t>48721</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>10,61%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>49548</t>
+          <t>49918</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>100667</t>
+          <t>97788</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>19,56%</t>
+          <t>19,0%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>85152</t>
+          <t>85373</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>142362</t>
+          <t>142070</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5970,12 +5970,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>14,62%</t>
+          <t>14,59%</t>
         </is>
       </c>
     </row>
@@ -5998,12 +5998,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>410975</t>
+          <t>410530</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>432277</t>
+          <t>431256</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>89,49%</t>
+          <t>89,39%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,13%</t>
+          <t>93,9%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>413965</t>
+          <t>416844</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>465084</t>
+          <t>464714</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>80,44%</t>
+          <t>81,0%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>90,37%</t>
+          <t>90,3%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>831520</t>
+          <t>831812</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>888730</t>
+          <t>888509</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>85,38%</t>
+          <t>85,41%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>91,26%</t>
+          <t>91,23%</t>
         </is>
       </c>
     </row>
@@ -6228,12 +6228,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>11138</t>
+          <t>11221</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>24289</t>
+          <t>23834</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6243,12 +6243,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>16,24%</t>
+          <t>15,94%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>14695</t>
+          <t>15064</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>31866</t>
+          <t>32130</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6278,12 +6278,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>17,38%</t>
+          <t>17,52%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>29490</t>
+          <t>29425</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>50117</t>
+          <t>49940</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6313,12 +6313,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>8,84%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>15,05%</t>
+          <t>15,0%</t>
         </is>
       </c>
     </row>
@@ -6341,12 +6341,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>125262</t>
+          <t>125717</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>138413</t>
+          <t>138330</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6356,12 +6356,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>83,76%</t>
+          <t>84,06%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>92,55%</t>
+          <t>92,5%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>151483</t>
+          <t>151219</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>168654</t>
+          <t>168285</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6391,12 +6391,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>82,62%</t>
+          <t>82,48%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>91,99%</t>
+          <t>91,78%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>282783</t>
+          <t>282960</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>303410</t>
+          <t>303475</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6426,12 +6426,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>84,95%</t>
+          <t>85,0%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>91,14%</t>
+          <t>91,16%</t>
         </is>
       </c>
     </row>
@@ -6571,12 +6571,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>48787</t>
+          <t>49163</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>83524</t>
+          <t>83139</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6586,12 +6586,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,59%</t>
+          <t>12,53%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6606,12 +6606,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>80646</t>
+          <t>80504</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>131983</t>
+          <t>133640</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6621,12 +6621,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,61%</t>
+          <t>10,59%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>17,37%</t>
+          <t>17,58%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6641,12 +6641,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>137982</t>
+          <t>138405</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>207159</t>
+          <t>202596</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6656,12 +6656,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>9,72%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>14,55%</t>
+          <t>14,23%</t>
         </is>
       </c>
     </row>
@@ -6684,12 +6684,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>579956</t>
+          <t>580341</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>614693</t>
+          <t>614317</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6699,12 +6699,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>87,41%</t>
+          <t>87,47%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>92,65%</t>
+          <t>92,59%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>628001</t>
+          <t>626344</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>679338</t>
+          <t>679480</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6734,12 +6734,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>82,63%</t>
+          <t>82,42%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>89,39%</t>
+          <t>89,41%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1216305</t>
+          <t>1220868</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1285482</t>
+          <t>1285059</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6769,12 +6769,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>85,45%</t>
+          <t>85,77%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>90,31%</t>
+          <t>90,28%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP08-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP08-Estudios-trans_orig.xlsx
@@ -544,7 +544,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +555,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -723,72 +723,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>10367</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>6175</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>15866</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>11,94%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>7,11%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>18,27%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>7818</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>3996</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>13204</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>4294</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>14130</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>8,6%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>4,4%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>14,53%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>10367</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>6105</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>16232</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>11,94%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>18,69%</t>
+          <t>15,55%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>12192</t>
+          <t>11781</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>26648</t>
+          <t>25544</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>14,37%</t>
         </is>
       </c>
     </row>
@@ -836,72 +836,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>76478</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>70979</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>80670</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>88,06%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>81,73%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>92,89%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>125</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>83049</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>77663</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>86871</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>76737</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>86573</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>91,4%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>85,47%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>95,6%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>115</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>76478</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>70613</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>80740</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>88,06%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>81,31%</t>
+          <t>84,45%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>92,97%</t>
+          <t>95,27%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>151064</t>
+          <t>152168</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>165520</t>
+          <t>165931</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>85,0%</t>
+          <t>85,63%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>93,14%</t>
+          <t>93,37%</t>
         </is>
       </c>
     </row>
@@ -949,57 +949,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>86845</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>86845</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>86845</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>136</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>90867</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>90867</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>90867</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>86845</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>86845</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>86845</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1066,72 +1066,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>53441</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>42705</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>65111</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>11,22%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>8,97%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>13,67%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>46</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>30560</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>22996</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>39833</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>22581</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>39532</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>7,34%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>5,53%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>9,57%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>53441</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>43465</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>64741</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>11,22%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>13,59%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>70963</t>
+          <t>70542</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>99720</t>
+          <t>98102</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>11,17%</t>
+          <t>10,99%</t>
         </is>
       </c>
     </row>
@@ -1179,72 +1179,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>638</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>422855</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>411185</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>433591</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>88,78%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>86,33%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>91,03%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>582</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>385527</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>376254</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>393091</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>376555</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>393506</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>92,66%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>90,43%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>94,47%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>638</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>422855</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>411555</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>432831</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>88,78%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>86,41%</t>
+          <t>90,5%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>90,87%</t>
+          <t>94,57%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>792663</t>
+          <t>794281</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>821420</t>
+          <t>821841</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>88,83%</t>
+          <t>89,01%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,05%</t>
+          <t>92,1%</t>
         </is>
       </c>
     </row>
@@ -1292,57 +1292,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>718</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>476296</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>476296</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>476296</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>628</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>416087</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>416087</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>416087</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>718</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>476296</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>476296</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>476296</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1409,72 +1409,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>19670</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>13601</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>27024</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>12,44%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>8,6%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>17,09%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>26</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>17866</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>12407</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>25374</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>11866</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>25261</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>10,26%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>7,13%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>14,58%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>19670</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>14054</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>27324</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>12,44%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>17,28%</t>
+          <t>14,51%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>28519</t>
+          <t>29127</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>47400</t>
+          <t>48049</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>14,27%</t>
+          <t>14,46%</t>
         </is>
       </c>
     </row>
@@ -1522,72 +1522,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>207</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>138468</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>131114</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>144537</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>87,56%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>82,91%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>91,4%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>228</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>156200</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>148692</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>161659</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>148805</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>162200</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>89,74%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>85,42%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>92,87%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>207</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>138468</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>130814</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>144084</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>87,56%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>82,72%</t>
+          <t>85,49%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>91,11%</t>
+          <t>93,18%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>284805</t>
+          <t>284156</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>303686</t>
+          <t>303078</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>85,73%</t>
+          <t>85,54%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>91,42%</t>
+          <t>91,23%</t>
         </is>
       </c>
     </row>
@@ -1635,57 +1635,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>236</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>158138</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>158138</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>158138</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>254</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>174066</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>174066</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>174066</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>236</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>158138</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>158138</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>158138</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1752,72 +1752,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>83478</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>68973</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>98232</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>11,57%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>9,56%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>13,62%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>83</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>56243</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>45465</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>68573</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>45625</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>69264</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>8,26%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>6,68%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>10,07%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>124</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>83478</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>68929</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>97324</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>11,57%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>13,49%</t>
+          <t>10,17%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>120248</t>
+          <t>122057</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>157045</t>
+          <t>158165</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>11,28%</t>
         </is>
       </c>
     </row>
@@ -1865,72 +1865,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>960</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>637801</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>623047</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>652306</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>88,43%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>86,38%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>90,44%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>935</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>624778</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>612448</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>635556</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>611757</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>635396</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>91,74%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>89,93%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>93,32%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>960</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>637801</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>623955</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>652350</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>88,43%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>86,51%</t>
+          <t>89,83%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>90,44%</t>
+          <t>93,3%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1245255</t>
+          <t>1244135</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1282052</t>
+          <t>1280243</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>88,8%</t>
+          <t>88,72%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>91,42%</t>
+          <t>91,3%</t>
         </is>
       </c>
     </row>
@@ -1978,57 +1978,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>1084</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>721279</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>721279</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>721279</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>1018</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>681021</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>681021</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>681021</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>1084</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>721279</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>721279</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>721279</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2147,7 +2147,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2158,7 +2158,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2326,72 +2326,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>11551</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>7018</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>17503</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>13,4%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>8,14%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>20,31%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>12746</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>8232</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>19062</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>8182</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>18492</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>13,8%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>8,91%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>20,64%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>11551</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>7111</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>17583</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>13,4%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>8,86%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>20,4%</t>
+          <t>20,02%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>17433</t>
+          <t>17130</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>33074</t>
+          <t>32667</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>9,59%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>18,52%</t>
+          <t>18,29%</t>
         </is>
       </c>
     </row>
@@ -2439,72 +2439,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>74641</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>68689</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>79174</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>86,6%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>79,69%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>91,86%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>115</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>79623</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>73307</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>84137</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>73877</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>84187</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>86,2%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>79,36%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>91,09%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>105</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>74641</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>68609</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>79081</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>86,6%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>79,6%</t>
+          <t>79,98%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>91,75%</t>
+          <t>91,14%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>145487</t>
+          <t>145894</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>161128</t>
+          <t>161431</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>81,48%</t>
+          <t>81,71%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>90,24%</t>
+          <t>90,41%</t>
         </is>
       </c>
     </row>
@@ -2552,57 +2552,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>121</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>86192</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>86192</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>86192</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>134</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>92369</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>92369</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>92369</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>121</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>86192</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>86192</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>86192</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -2669,72 +2669,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>70395</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>57676</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>82804</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>14,24%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>11,66%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>16,75%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>80</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>54883</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>44663</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>67524</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>43962</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>66639</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>12,14%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>9,88%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>14,93%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>70395</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>58141</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>83638</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>14,24%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11,76%</t>
+          <t>9,72%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>16,92%</t>
+          <t>14,74%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>110172</t>
+          <t>109299</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>144729</t>
+          <t>142757</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>11,55%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>15,29%</t>
+          <t>15,08%</t>
         </is>
       </c>
     </row>
@@ -2782,72 +2782,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>608</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>424051</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>411642</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>436770</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>85,76%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>83,25%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>88,34%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>575</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>397327</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>384686</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>407547</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>385571</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>408248</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>87,86%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>85,07%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>90,12%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>608</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>424051</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>410808</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>436305</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>85,76%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>83,08%</t>
+          <t>85,26%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>88,24%</t>
+          <t>90,28%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>801927</t>
+          <t>803899</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>836484</t>
+          <t>837357</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>84,71%</t>
+          <t>84,92%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>88,36%</t>
+          <t>88,45%</t>
         </is>
       </c>
     </row>
@@ -2895,57 +2895,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>708</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>494446</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>494446</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>494446</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>655</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>452210</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>452210</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>452210</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>708</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>494446</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>494446</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>494446</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3012,72 +3012,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>20474</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>13680</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>28061</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>11,89%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>7,94%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>16,29%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>23</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>15240</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>9888</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>21819</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>10538</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>22878</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>9,18%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>5,95%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>13,14%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>20474</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>13433</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>28413</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>11,89%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>16,5%</t>
+          <t>13,78%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>27316</t>
+          <t>26831</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>45110</t>
+          <t>45635</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>13,33%</t>
+          <t>13,49%</t>
         </is>
       </c>
     </row>
@@ -3125,72 +3125,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>216</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>151754</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>144167</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>158548</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>88,11%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>83,71%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>92,06%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>212</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>150838</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>144259</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>156190</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>143200</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>155540</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>90,82%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>86,86%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>94,05%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>216</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>151754</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>143815</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>158795</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>88,11%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>83,5%</t>
+          <t>86,22%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>92,2%</t>
+          <t>93,65%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>293197</t>
+          <t>292672</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>310991</t>
+          <t>311476</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>86,67%</t>
+          <t>86,51%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>91,93%</t>
+          <t>92,07%</t>
         </is>
       </c>
     </row>
@@ -3238,57 +3238,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>244</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>172228</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>172228</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>172228</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>235</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>166078</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>166078</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>166078</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>244</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>172228</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>172228</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>172228</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3355,72 +3355,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>102419</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>88371</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>118979</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>13,6%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>11,74%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>15,8%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>122</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>82869</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>69593</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>97242</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>70360</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>96227</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>11,66%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>9,79%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>13,68%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>144</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>102419</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>87653</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>118574</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>13,6%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>9,9%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,75%</t>
+          <t>13,54%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>165828</t>
+          <t>165192</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>207723</t>
+          <t>206381</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>11,29%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>14,19%</t>
+          <t>14,1%</t>
         </is>
       </c>
     </row>
@@ -3468,72 +3468,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>650447</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>633887</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>664495</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>86,4%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>84,2%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>88,26%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>902</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>627788</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>613415</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>641064</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>614430</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>640297</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>88,34%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>86,32%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>90,21%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>929</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>650447</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>634292</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>665213</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>86,4%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>84,25%</t>
+          <t>86,46%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>88,36%</t>
+          <t>90,1%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1255800</t>
+          <t>1257142</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1297695</t>
+          <t>1298331</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>85,81%</t>
+          <t>85,9%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>88,67%</t>
+          <t>88,71%</t>
         </is>
       </c>
     </row>
@@ -3581,57 +3581,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>1073</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>752866</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>752866</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>752866</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>1024</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>710657</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>710657</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>710657</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>1073</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>752866</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>752866</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>752866</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -3750,7 +3750,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -3761,7 +3761,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -3929,72 +3929,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>2773</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>771</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>6987</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>4,04%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>1,12%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>10,18%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>4449</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>1836</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>8526</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>1952</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>9295</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>7,49%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>3,09%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>14,36%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>2773</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>686</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>6799</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>4,04%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>15,65%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3789</t>
+          <t>3685</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>12610</t>
+          <t>12849</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>10,04%</t>
         </is>
       </c>
     </row>
@@ -4042,72 +4042,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>65841</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>61627</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>67843</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>95,96%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>89,82%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>98,88%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>82</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>54929</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>50852</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>57542</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>50083</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>57426</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>92,51%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>85,64%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>96,91%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>65841</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>61815</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>67928</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>95,96%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>90,09%</t>
+          <t>84,35%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,0%</t>
+          <t>96,71%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>115383</t>
+          <t>115144</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>124204</t>
+          <t>124308</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>90,15%</t>
+          <t>89,96%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,04%</t>
+          <t>97,12%</t>
         </is>
       </c>
     </row>
@@ -4155,57 +4155,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>68614</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>68614</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>68614</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>89</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>59378</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>59378</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>59378</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>68614</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>68614</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>68614</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4272,72 +4272,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>38515</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>29921</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>49463</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>7,92%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>6,15%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>10,17%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>48</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>31600</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>23868</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>41580</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>23274</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>41219</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>6,71%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>5,07%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>8,83%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>38515</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>29445</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>50360</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>7,92%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>57677</t>
+          <t>57646</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>84476</t>
+          <t>84411</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4385,72 +4385,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>637</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>447826</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>436878</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>456420</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>92,08%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>89,83%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>93,85%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>664</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>439448</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>429468</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>447180</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>429829</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>447774</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>93,29%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>91,17%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>94,93%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>637</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>447826</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>435981</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>456896</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>92,08%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>89,65%</t>
+          <t>91,25%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,95%</t>
+          <t>95,06%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>872914</t>
+          <t>872979</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>899713</t>
+          <t>899744</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4498,57 +4498,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>692</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>486341</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>486341</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>486341</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>712</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>471048</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>471048</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>471048</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>692</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>486341</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>486341</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>486341</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4615,72 +4615,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>10159</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>5898</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>16109</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>5,44%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>3,16%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>8,62%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>11597</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>6974</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>17652</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>7391</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>18016</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>6,75%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>4,06%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>10,27%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>10159</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>5904</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>16546</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>5,44%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>10,49%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>14610</t>
+          <t>15773</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>29946</t>
+          <t>30016</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,37%</t>
         </is>
       </c>
     </row>
@@ -4728,72 +4728,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>255</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>176657</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>170707</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>180918</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>94,56%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>91,38%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>96,84%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>239</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>160205</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>154150</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>164828</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>153786</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>164411</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>93,25%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>89,73%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>95,94%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>255</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>176657</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>170270</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>180912</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>94,56%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>91,14%</t>
+          <t>89,51%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,84%</t>
+          <t>95,7%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>328672</t>
+          <t>328602</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>344008</t>
+          <t>342845</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>91,65%</t>
+          <t>91,63%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,93%</t>
+          <t>95,6%</t>
         </is>
       </c>
     </row>
@@ -4841,57 +4841,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>270</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>186816</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>186816</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>186816</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>257</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>171802</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>171802</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>171802</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>270</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>186816</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>186816</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>186816</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4958,72 +4958,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>51447</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>41347</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>63119</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>6,94%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>5,57%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>8,51%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>73</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>47647</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>37234</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>59554</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>36956</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>59632</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>6,79%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>5,3%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>8,48%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>51447</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>40454</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>62554</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>6,94%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>8,49%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>83244</t>
+          <t>84660</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>115865</t>
+          <t>116464</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>8,07%</t>
         </is>
       </c>
     </row>
@@ -5071,72 +5071,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>987</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>690325</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>678653</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>700425</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>93,06%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>91,49%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>94,43%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>985</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>654581</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>642674</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>664994</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>642596</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>665272</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>93,21%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>91,52%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>94,7%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>987</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>690325</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>679218</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>701318</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>93,06%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,57%</t>
+          <t>91,51%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,55%</t>
+          <t>94,74%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1328135</t>
+          <t>1327536</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1360756</t>
+          <t>1359340</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,98%</t>
+          <t>91,93%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,24%</t>
+          <t>94,14%</t>
         </is>
       </c>
     </row>
@@ -5184,57 +5184,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>1061</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>741772</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>741772</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>741772</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>1058</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>702228</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>702228</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>702228</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>1061</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>741772</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>741772</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>741772</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5353,7 +5353,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -5364,7 +5364,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -5532,72 +5532,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>9664</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>5776</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>15240</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>17,04%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>10,18%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>26,86%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>9382</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>2628</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>24815</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>17,16%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>4,81%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>45,38%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>10908</t>
+          <t>4383</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6143</t>
+          <t>1892</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>16606</t>
+          <t>8745</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>17,59%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>26,78%</t>
+          <t>18,7%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5607,32 +5607,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>20290</t>
+          <t>14048</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>12397</t>
+          <t>8839</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>34551</t>
+          <t>21238</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>17,39%</t>
+          <t>13,57%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>29,61%</t>
+          <t>20,52%</t>
         </is>
       </c>
     </row>
@@ -5645,72 +5645,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>47068</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>41492</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>50956</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>82,96%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>73,14%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>89,82%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>62</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>45296</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>29863</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>52050</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>82,84%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>54,62%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>95,19%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>51096</t>
+          <t>42375</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>45398</t>
+          <t>38013</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>55861</t>
+          <t>44866</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>82,41%</t>
+          <t>90,63%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>73,22%</t>
+          <t>81,3%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>90,09%</t>
+          <t>95,95%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5720,32 +5720,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>96392</t>
+          <t>89442</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>82131</t>
+          <t>82252</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>104285</t>
+          <t>94651</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>82,61%</t>
+          <t>86,43%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>70,39%</t>
+          <t>79,48%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>89,38%</t>
+          <t>91,46%</t>
         </is>
       </c>
     </row>
@@ -5758,57 +5758,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>56732</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>56732</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>56732</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>69</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>54678</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>54678</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>54678</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>62004</t>
+          <t>46758</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>62004</t>
+          <t>46758</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>62004</t>
+          <t>46758</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5833,17 +5833,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>116682</t>
+          <t>103490</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>116682</t>
+          <t>103490</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>116682</t>
+          <t>103490</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5875,72 +5875,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>59427</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>45234</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>87264</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>12,55%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>9,55%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>18,43%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>56</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>37573</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>27995</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>48721</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>8,18%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>6,1%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>10,61%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>65817</t>
+          <t>37486</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>49918</t>
+          <t>28748</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>97788</t>
+          <t>47686</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>8,69%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>19,0%</t>
+          <t>11,06%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5950,32 +5950,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>103390</t>
+          <t>96913</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>85373</t>
+          <t>80204</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>142070</t>
+          <t>122902</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>10,71%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>8,87%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>14,59%</t>
+          <t>13,58%</t>
         </is>
       </c>
     </row>
@@ -5988,72 +5988,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>575</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>414047</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>386210</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>428240</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>87,45%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>81,57%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>90,45%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>585</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>421678</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>410530</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>431256</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>91,82%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>89,39%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>93,9%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>575</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>448815</t>
+          <t>393731</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>416844</t>
+          <t>383531</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>464714</t>
+          <t>402469</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>87,21%</t>
+          <t>91,31%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>81,0%</t>
+          <t>88,94%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>90,3%</t>
+          <t>93,33%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6063,32 +6063,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>870492</t>
+          <t>807778</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>831812</t>
+          <t>781789</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>888509</t>
+          <t>824487</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>89,38%</t>
+          <t>89,29%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>85,41%</t>
+          <t>86,42%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>91,23%</t>
+          <t>91,13%</t>
         </is>
       </c>
     </row>
@@ -6101,57 +6101,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>654</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>473474</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>473474</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>473474</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>641</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>459251</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>459251</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>459251</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>654</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>514632</t>
+          <t>431217</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>514632</t>
+          <t>431217</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>514632</t>
+          <t>431217</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6176,17 +6176,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>973882</t>
+          <t>904691</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>973882</t>
+          <t>904691</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>973882</t>
+          <t>904691</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6223,32 +6223,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>16593</t>
+          <t>19779</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>11221</t>
+          <t>13229</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>23834</t>
+          <t>28665</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>11,74%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>15,94%</t>
+          <t>17,02%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6258,32 +6258,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>22304</t>
+          <t>17213</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>15064</t>
+          <t>11436</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>32130</t>
+          <t>25167</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>11,48%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>17,52%</t>
+          <t>16,78%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6293,32 +6293,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>38897</t>
+          <t>36993</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>29425</t>
+          <t>27583</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>49940</t>
+          <t>47964</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>11,62%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>15,06%</t>
         </is>
       </c>
     </row>
@@ -6331,72 +6331,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>212</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>148640</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>139754</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>155190</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>88,26%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>82,98%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>92,15%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>204</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>132958</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>125717</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>138330</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>88,9%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>84,06%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>92,5%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>212</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>161045</t>
+          <t>132763</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>151219</t>
+          <t>124809</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>168285</t>
+          <t>138540</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>87,84%</t>
+          <t>88,52%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>82,48%</t>
+          <t>83,22%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>91,78%</t>
+          <t>92,38%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6406,32 +6406,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>294003</t>
+          <t>281402</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>282960</t>
+          <t>270431</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>303475</t>
+          <t>290812</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>88,32%</t>
+          <t>88,38%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>85,0%</t>
+          <t>84,94%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>91,16%</t>
+          <t>91,34%</t>
         </is>
       </c>
     </row>
@@ -6444,57 +6444,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>238</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>168419</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>168419</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>168419</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>230</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>149551</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>149551</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>149551</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>238</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>183349</t>
+          <t>149976</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>183349</t>
+          <t>149976</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>183349</t>
+          <t>149976</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6519,17 +6519,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>332900</t>
+          <t>318395</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>332900</t>
+          <t>318395</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>332900</t>
+          <t>318395</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6561,72 +6561,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>88871</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>71419</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>114800</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>12,72%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>10,22%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>16,43%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>89</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>63548</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>49163</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>83139</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>9,58%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>7,41%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>12,53%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>99029</t>
+          <t>59082</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>80504</t>
+          <t>47230</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>133640</t>
+          <t>72252</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>13,03%</t>
+          <t>9,41%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>17,58%</t>
+          <t>11,51%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6636,32 +6636,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>162578</t>
+          <t>147953</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>138405</t>
+          <t>125466</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>202596</t>
+          <t>177545</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>11,15%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>9,46%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>14,23%</t>
+          <t>13,38%</t>
         </is>
       </c>
     </row>
@@ -6674,72 +6674,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>855</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>609754</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>583825</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>627206</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>87,28%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>83,57%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>89,78%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>851</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>599932</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>580341</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>614317</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>90,42%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>87,47%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>92,59%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>855</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>660955</t>
+          <t>568869</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>626344</t>
+          <t>555699</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>679480</t>
+          <t>580721</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>86,97%</t>
+          <t>90,59%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>82,42%</t>
+          <t>88,49%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>89,41%</t>
+          <t>92,48%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6749,32 +6749,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1260886</t>
+          <t>1178623</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1220868</t>
+          <t>1149031</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1285059</t>
+          <t>1201110</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>88,58%</t>
+          <t>88,85%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>85,77%</t>
+          <t>86,62%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>90,28%</t>
+          <t>90,54%</t>
         </is>
       </c>
     </row>
@@ -6787,57 +6787,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>975</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>698625</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>698625</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>698625</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>940</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>663480</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>663480</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>663480</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>975</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>759984</t>
+          <t>627951</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>759984</t>
+          <t>627951</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>759984</t>
+          <t>627951</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6862,17 +6862,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1423464</t>
+          <t>1326576</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1423464</t>
+          <t>1326576</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1423464</t>
+          <t>1326576</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
